--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>44473</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1080,7 +1080,7 @@
         <v>45708</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1193,7 +1193,7 @@
         <v>44648</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1300,7 +1300,7 @@
         <v>44581</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1411,7 +1411,7 @@
         <v>44610</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>45097</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1627,7 +1627,7 @@
         <v>45203</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1733,7 +1733,7 @@
         <v>44484</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>44524</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1950,7 +1950,7 @@
         <v>44880</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2056,7 +2056,7 @@
         <v>45330</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2162,7 +2162,7 @@
         <v>44628</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2272,7 +2272,7 @@
         <v>46009</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>45215</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45441</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2604,7 +2604,7 @@
         <v>45015</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45201</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>44546</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2929,7 +2929,7 @@
         <v>44461</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45435</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>45035</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3253,7 +3253,7 @@
         <v>45705</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44972</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3463,7 +3463,7 @@
         <v>45181</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3568,7 +3568,7 @@
         <v>45947</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3673,7 +3673,7 @@
         <v>45015</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3782,7 +3782,7 @@
         <v>45989</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3887,7 +3887,7 @@
         <v>45162</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45761</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>46090</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>45210</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>45112</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4427,7 +4427,7 @@
         <v>45716</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45821</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4647,7 +4647,7 @@
         <v>45821</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4757,7 +4757,7 @@
         <v>45716</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4862,7 +4862,7 @@
         <v>45797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4972,7 +4972,7 @@
         <v>45821</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5082,7 +5082,7 @@
         <v>45703</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>45703</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
         <v>44619</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5375,7 +5375,7 @@
         <v>44461</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5448,7 +5448,7 @@
         <v>44574</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5521,7 +5521,7 @@
         <v>44746</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5594,7 +5594,7 @@
         <v>44840</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5667,7 +5667,7 @@
         <v>44852</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5740,7 +5740,7 @@
         <v>44473</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5813,7 +5813,7 @@
         <v>44460</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5886,7 +5886,7 @@
         <v>44461</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44539</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6032,7 +6032,7 @@
         <v>44523</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44614</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>44766</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
         <v>44880</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6329,7 +6329,7 @@
         <v>44496</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>44758</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44693</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>44649</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6626,7 +6626,7 @@
         <v>44571</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6699,7 +6699,7 @@
         <v>44880</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6772,7 +6772,7 @@
         <v>44526</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>44523</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6923,7 +6923,7 @@
         <v>44592</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>44530</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45590</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7147,7 +7147,7 @@
         <v>45674</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>44843</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45677</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7366,7 +7366,7 @@
         <v>44830</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7439,7 +7439,7 @@
         <v>44574</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7512,7 +7512,7 @@
         <v>45590</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7585,7 +7585,7 @@
         <v>45397</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7658,7 +7658,7 @@
         <v>45705</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7731,7 +7731,7 @@
         <v>44629</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>45324</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44630</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7955,7 +7955,7 @@
         <v>44830</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>45470</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8106,7 +8106,7 @@
         <v>45097</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8179,7 +8179,7 @@
         <v>45600</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8252,7 +8252,7 @@
         <v>44847</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8325,7 +8325,7 @@
         <v>44521</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8398,7 +8398,7 @@
         <v>45210</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8471,7 +8471,7 @@
         <v>45210</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8544,7 +8544,7 @@
         <v>44746</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44942</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44693</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44971</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44536</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44993</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>45240</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>44797</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9133,7 +9133,7 @@
         <v>45268</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9206,7 +9206,7 @@
         <v>45373</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9279,7 +9279,7 @@
         <v>45163</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45265</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>45560</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>44746</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>44746</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>44536</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45393</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>45343</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>44901</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9961,7 +9961,7 @@
         <v>44883</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10039,7 +10039,7 @@
         <v>45744</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10112,7 +10112,7 @@
         <v>45199</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44958</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45548</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>44964</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10404,7 +10404,7 @@
         <v>45201</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44994</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10550,7 +10550,7 @@
         <v>45764</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>44774</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10696,7 +10696,7 @@
         <v>44937</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44645</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10847,7 +10847,7 @@
         <v>44836</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10920,7 +10920,7 @@
         <v>45887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10998,7 +10998,7 @@
         <v>45722</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11071,7 +11071,7 @@
         <v>45170</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11144,7 +11144,7 @@
         <v>45222</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11217,7 +11217,7 @@
         <v>44843</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44865</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>44638</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11436,7 +11436,7 @@
         <v>45167</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         <v>45443</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>44936</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>45887</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45887</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11811,7 +11811,7 @@
         <v>45887</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11889,7 +11889,7 @@
         <v>44812</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>45201</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>45203</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44986</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>45897</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44620</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12327,7 +12327,7 @@
         <v>45211</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12400,7 +12400,7 @@
         <v>45875</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12473,7 +12473,7 @@
         <v>45560</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12551,7 +12551,7 @@
         <v>45909</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12624,7 +12624,7 @@
         <v>45211</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12697,7 +12697,7 @@
         <v>45266</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>45909</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>45728</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>45911</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44974</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13067,7 +13067,7 @@
         <v>44974</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>45070</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13218,7 +13218,7 @@
         <v>45131</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>45664</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44965</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13437,7 +13437,7 @@
         <v>44994</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>45033</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>45558</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13656,7 +13656,7 @@
         <v>45210</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45210</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13802,7 +13802,7 @@
         <v>44943</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13875,7 +13875,7 @@
         <v>45343</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13948,7 +13948,7 @@
         <v>44943</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14021,7 +14021,7 @@
         <v>45135</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14094,7 +14094,7 @@
         <v>44935</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14167,7 +14167,7 @@
         <v>45384</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14240,7 +14240,7 @@
         <v>45720</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14313,7 +14313,7 @@
         <v>45947</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45006</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45225</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45188</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14610,7 +14610,7 @@
         <v>45329</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14683,7 +14683,7 @@
         <v>44739</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14761,7 +14761,7 @@
         <v>45761</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14834,7 +14834,7 @@
         <v>45958</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>45958</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>45958</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45324</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15131,7 +15131,7 @@
         <v>44756</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44936</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15277,7 +15277,7 @@
         <v>45965</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45639</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45966</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>45535</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45243</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45412</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45412</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>45972</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>45544</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15939,7 +15939,7 @@
         <v>45271</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45268</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         <v>45530</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>44572</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16236,7 +16236,7 @@
         <v>44903</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16309,7 +16309,7 @@
         <v>46157</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
         <v>46157</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16455,7 +16455,7 @@
         <v>46142</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16533,7 +16533,7 @@
         <v>45271</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16606,7 +16606,7 @@
         <v>44986</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>45217</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16752,7 +16752,7 @@
         <v>44930</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45330</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16898,7 +16898,7 @@
         <v>46163</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16971,7 +16971,7 @@
         <v>46163</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17044,7 +17044,7 @@
         <v>46163</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17122,7 +17122,7 @@
         <v>45015</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17195,7 +17195,7 @@
         <v>44876</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17273,7 +17273,7 @@
         <v>44900</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17346,7 +17346,7 @@
         <v>46003</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17419,7 +17419,7 @@
         <v>44812</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>44957</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>45371</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17638,7 +17638,7 @@
         <v>46008</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17716,7 +17716,7 @@
         <v>44622</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17789,7 +17789,7 @@
         <v>45982</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17862,7 +17862,7 @@
         <v>45516</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>46169</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45271</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45268</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46029</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18232,7 +18232,7 @@
         <v>46029</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18310,7 +18310,7 @@
         <v>45210</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18383,7 +18383,7 @@
         <v>46171</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18461,7 +18461,7 @@
         <v>46171</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18539,7 +18539,7 @@
         <v>46171</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18617,7 +18617,7 @@
         <v>45350</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18690,7 +18690,7 @@
         <v>46042</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18763,7 +18763,7 @@
         <v>46171</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18841,7 +18841,7 @@
         <v>45210</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>46050</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>46051</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19065,7 +19065,7 @@
         <v>44993</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19138,7 +19138,7 @@
         <v>45702</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>46057</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>44890</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45761</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19440,7 +19440,7 @@
         <v>46061</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19513,7 +19513,7 @@
         <v>44973</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>44614</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19664,7 +19664,7 @@
         <v>46071</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19737,7 +19737,7 @@
         <v>46071</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>44816</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19883,7 +19883,7 @@
         <v>46071</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
         <v>46077</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>45583</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>44943</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20175,7 +20175,7 @@
         <v>46080</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>44981</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20321,7 +20321,7 @@
         <v>45210</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20394,7 +20394,7 @@
         <v>46185</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>46188</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20545,7 +20545,7 @@
         <v>44756</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20618,7 +20618,7 @@
         <v>45412</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20691,7 +20691,7 @@
         <v>45412</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20764,7 +20764,7 @@
         <v>46090</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20842,7 +20842,7 @@
         <v>46090</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>44965</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>44496</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45200</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45590</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45709</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21290,7 +21290,7 @@
         <v>46100</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45211</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45114</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21509,7 +21509,7 @@
         <v>44489</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>45289</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21665,7 +21665,7 @@
         <v>46119</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21738,7 +21738,7 @@
         <v>45548</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45211</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21884,7 +21884,7 @@
         <v>44881</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21957,7 +21957,7 @@
         <v>45460</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>45524</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22103,7 +22103,7 @@
         <v>44553</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22176,7 +22176,7 @@
         <v>45590</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>44649</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22327,7 +22327,7 @@
         <v>44617</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22405,7 +22405,7 @@
         <v>46205</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22478,7 +22478,7 @@
         <v>45097</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22556,7 +22556,7 @@
         <v>46199</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22629,7 +22629,7 @@
         <v>46199</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45706</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22775,7 +22775,7 @@
         <v>45722</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>44616</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>46199</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>46199</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>46206</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>45590</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23228,7 +23228,7 @@
         <v>45070</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23301,7 +23301,7 @@
         <v>45751</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>44999</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23447,7 +23447,7 @@
         <v>45200</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23520,7 +23520,7 @@
         <v>45528</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23593,7 +23593,7 @@
         <v>46253</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23666,7 +23666,7 @@
         <v>45210</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23739,7 +23739,7 @@
         <v>44848</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45260</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23885,7 +23885,7 @@
         <v>45393</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45516</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24031,7 +24031,7 @@
         <v>44746</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24104,7 +24104,7 @@
         <v>46261</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>46261</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24260,7 +24260,7 @@
         <v>45516</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24333,7 +24333,7 @@
         <v>45674</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24406,7 +24406,7 @@
         <v>46262</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24479,7 +24479,7 @@
         <v>44917</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>46262</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24625,7 +24625,7 @@
         <v>45691</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24698,7 +24698,7 @@
         <v>45265</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>45211</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>45720</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>45299</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>45720</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>45684</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>45307</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>45516</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>45590</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45545</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25438,7 +25438,7 @@
         <v>44521</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25511,7 +25511,7 @@
         <v>45705</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25584,7 +25584,7 @@
         <v>45616</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25657,7 +25657,7 @@
         <v>45211</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45728</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25808,7 +25808,7 @@
         <v>45502</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>45709</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>45790</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45716</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45331</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>45610</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45600</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45798</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26397,7 +26397,7 @@
         <v>45798</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26475,7 +26475,7 @@
         <v>45798</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26553,7 +26553,7 @@
         <v>45804</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26631,7 +26631,7 @@
         <v>45804</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26704,7 +26704,7 @@
         <v>45804</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26777,7 +26777,7 @@
         <v>45754</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26850,7 +26850,7 @@
         <v>45817</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26923,7 +26923,7 @@
         <v>45818</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45819</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27069,7 +27069,7 @@
         <v>45821</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27142,7 +27142,7 @@
         <v>45820</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>45820</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27288,7 +27288,7 @@
         <v>45827</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>45832</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45873</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27507,7 +27507,7 @@
         <v>45875</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27585,7 +27585,7 @@
         <v>45618</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45757</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27741,7 +27741,7 @@
         <v>46064</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>

--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>44581</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>44610</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45215</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45441</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44484</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45015</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>46009</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44880</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45330</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45201</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45097</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>44628</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44546</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>46090</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45705</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45947</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45989</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45821</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>45821</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>45210</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>45162</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45761</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>44972</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45015</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>45035</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45435</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>45181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45716</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>45821</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45703</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45703</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44619</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44574</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44840</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44852</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44746</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44473</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44523</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44614</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44766</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44880</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44496</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44758</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44693</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44649</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44571</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44880</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44526</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44523</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>45709</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45343</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45211</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45299</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45412</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>45412</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44848</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45097</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>45373</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>45460</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44812</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45393</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44883</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45210</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44553</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45131</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>44812</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>45516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>45600</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>45443</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45265</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>45271</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45268</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45271</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44489</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>46029</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>46029</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45610</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>45798</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45798</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45798</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44521</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>45887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45887</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>45887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45243</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46042</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44903</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45590</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>45674</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>46050</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>46051</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>45909</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>46057</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>45911</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>46061</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45260</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>45516</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45516</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>45804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>44999</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45804</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>46071</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45804</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>46071</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>46071</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44994</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45033</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>46077</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45240</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>44865</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>45560</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>46080</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44936</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44876</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45590</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>46090</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45744</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45548</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>44936</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45754</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>46100</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45199</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45720</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45947</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>44943</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>44739</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44993</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45958</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45350</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>44830</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45958</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45015</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46119</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44971</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>44614</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45966</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>45965</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44958</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44965</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45006</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45972</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45706</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44986</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45817</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44993</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44881</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45818</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45664</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45722</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45728</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45167</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45544</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>46003</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45820</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45210</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45210</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>46008</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45560</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>45819</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44830</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45821</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45211</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45875</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45170</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44965</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45827</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44746</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44843</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45070</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>44847</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45210</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45535</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>44943</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44901</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>46142</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>44836</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>46157</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>46157</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44994</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45211</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>46163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>46163</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>46163</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45832</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45982</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45200</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45393</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>45268</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>46171</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>46171</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45163</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>46171</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45412</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45412</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>46171</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45397</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44620</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45720</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>44536</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45873</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46185</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45470</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44630</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>46188</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45548</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45751</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45330</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45875</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45590</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45217</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>46199</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>46199</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>46199</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>46205</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>46199</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44649</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>44629</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>46206</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>44645</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44638</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>45200</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45691</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>46253</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45761</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>44574</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>45210</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45210</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45764</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>44900</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45188</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>46261</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46261</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>46262</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>46262</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44746</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44746</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44746</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44797</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45265</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45761</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>44693</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45324</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>45211</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45583</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45135</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45528</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44756</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45201</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>46288</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>46288</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>46288</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>46288</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45268</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>46288</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>44973</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>46288</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>46288</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45590</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>46289</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>44496</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44964</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>45203</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44572</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44617</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44930</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46290</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>44816</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>44937</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45674</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45210</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45114</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45705</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>44917</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45558</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45639</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>44622</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45225</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44616</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45324</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>45530</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>44536</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>45097</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>44981</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45329</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45677</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45201</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44974</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>44974</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45211</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>44843</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44935</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45371</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45266</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45590</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>44890</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>45070</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45289</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>44942</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44774</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44756</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45600</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45222</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44957</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45343</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45722</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45702</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45271</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45524</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45384</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45720</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45684</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45516</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45545</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45307</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45590</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45790</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>44521</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45502</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45716</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45331</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>45728</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45616</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45709</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45705</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45618</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45757</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>46064</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>

--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>44581</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>44610</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>45215</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>45441</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>44484</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
         <v>45015</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2068,7 +2068,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2179,7 +2179,7 @@
         <v>46009</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2290,7 +2290,7 @@
         <v>44880</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2396,7 +2396,7 @@
         <v>45330</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>45203</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2608,7 +2608,7 @@
         <v>45201</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2718,7 +2718,7 @@
         <v>45097</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>44628</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44546</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>46090</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45705</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>45947</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3359,7 +3359,7 @@
         <v>45989</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45821</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3574,7 +3574,7 @@
         <v>45821</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>45210</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3789,7 +3789,7 @@
         <v>45162</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>45761</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>44972</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45112</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45015</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>45035</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45435</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4543,7 +4543,7 @@
         <v>45181</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4758,7 +4758,7 @@
         <v>45716</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45797</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>45821</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45703</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>45703</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>44619</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44574</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5449,7 +5449,7 @@
         <v>44840</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>44852</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5595,7 +5595,7 @@
         <v>44746</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5668,7 +5668,7 @@
         <v>44473</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5741,7 +5741,7 @@
         <v>44539</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5814,7 +5814,7 @@
         <v>44523</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5887,7 +5887,7 @@
         <v>44614</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5965,7 +5965,7 @@
         <v>44766</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6038,7 +6038,7 @@
         <v>44880</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>44496</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6189,7 +6189,7 @@
         <v>44758</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>44693</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6335,7 +6335,7 @@
         <v>44649</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>44571</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>44880</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6554,7 +6554,7 @@
         <v>44526</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6632,7 +6632,7 @@
         <v>44523</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6705,7 +6705,7 @@
         <v>44592</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6778,7 +6778,7 @@
         <v>44530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6851,7 +6851,7 @@
         <v>45709</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6924,7 +6924,7 @@
         <v>45343</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6997,7 +6997,7 @@
         <v>45211</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7070,7 +7070,7 @@
         <v>45299</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7143,7 +7143,7 @@
         <v>45412</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>45412</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7289,7 +7289,7 @@
         <v>44848</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7362,7 +7362,7 @@
         <v>45097</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7435,7 +7435,7 @@
         <v>45373</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>45460</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7581,7 +7581,7 @@
         <v>44812</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7654,7 +7654,7 @@
         <v>45393</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>44883</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7805,7 +7805,7 @@
         <v>45210</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7878,7 +7878,7 @@
         <v>44553</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7951,7 +7951,7 @@
         <v>45131</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -8024,7 +8024,7 @@
         <v>44812</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8097,7 +8097,7 @@
         <v>45516</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8170,7 +8170,7 @@
         <v>45600</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>45443</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8316,7 +8316,7 @@
         <v>45265</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8394,7 +8394,7 @@
         <v>45271</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45268</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45271</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8613,7 +8613,7 @@
         <v>44489</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8691,7 +8691,7 @@
         <v>46029</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8769,7 +8769,7 @@
         <v>46029</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8847,7 +8847,7 @@
         <v>45610</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8920,7 +8920,7 @@
         <v>45798</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8998,7 +8998,7 @@
         <v>45798</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9076,7 +9076,7 @@
         <v>45798</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9154,7 +9154,7 @@
         <v>44521</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9227,7 +9227,7 @@
         <v>45887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>45887</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45887</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>45887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>45243</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9612,7 +9612,7 @@
         <v>46042</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>45897</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44903</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>45590</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9909,7 +9909,7 @@
         <v>45674</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9982,7 +9982,7 @@
         <v>46050</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -10055,7 +10055,7 @@
         <v>46051</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>45909</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>45909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>46057</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10357,7 +10357,7 @@
         <v>45911</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>46061</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10503,7 +10503,7 @@
         <v>45260</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10576,7 +10576,7 @@
         <v>45516</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10649,7 +10649,7 @@
         <v>45516</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10722,7 +10722,7 @@
         <v>45804</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10800,7 +10800,7 @@
         <v>44999</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
         <v>45804</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>46071</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>45804</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>46071</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11165,7 +11165,7 @@
         <v>46071</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44994</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11311,7 +11311,7 @@
         <v>45033</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11384,7 +11384,7 @@
         <v>46077</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11457,7 +11457,7 @@
         <v>45240</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11530,7 +11530,7 @@
         <v>44865</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11603,7 +11603,7 @@
         <v>45560</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>46080</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11754,7 +11754,7 @@
         <v>44936</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11827,7 +11827,7 @@
         <v>44876</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11905,7 +11905,7 @@
         <v>45590</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11983,7 +11983,7 @@
         <v>46090</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12061,7 +12061,7 @@
         <v>45210</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12134,7 +12134,7 @@
         <v>45744</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12207,7 +12207,7 @@
         <v>45548</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12280,7 +12280,7 @@
         <v>44936</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12353,7 +12353,7 @@
         <v>45754</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12426,7 +12426,7 @@
         <v>46100</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>45199</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12572,7 +12572,7 @@
         <v>45720</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12645,7 +12645,7 @@
         <v>45947</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12718,7 +12718,7 @@
         <v>44943</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12791,7 +12791,7 @@
         <v>44739</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44993</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12947,7 +12947,7 @@
         <v>45958</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -13020,7 +13020,7 @@
         <v>45350</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13093,7 +13093,7 @@
         <v>44830</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13166,7 +13166,7 @@
         <v>45958</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13239,7 +13239,7 @@
         <v>45015</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13312,7 +13312,7 @@
         <v>45958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13385,7 +13385,7 @@
         <v>46119</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13458,7 +13458,7 @@
         <v>44971</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13531,7 +13531,7 @@
         <v>44614</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13609,7 +13609,7 @@
         <v>45966</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>45965</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13755,7 +13755,7 @@
         <v>44958</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13828,7 +13828,7 @@
         <v>44965</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13901,7 +13901,7 @@
         <v>45006</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13974,7 +13974,7 @@
         <v>45972</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14052,7 +14052,7 @@
         <v>45706</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>44986</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14198,7 +14198,7 @@
         <v>45817</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14271,7 +14271,7 @@
         <v>44993</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14344,7 +14344,7 @@
         <v>44881</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14417,7 +14417,7 @@
         <v>45818</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14490,7 +14490,7 @@
         <v>45664</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14563,7 +14563,7 @@
         <v>45722</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
         <v>44986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>45728</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14787,7 +14787,7 @@
         <v>45167</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>45544</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14933,7 +14933,7 @@
         <v>46003</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -15006,7 +15006,7 @@
         <v>45820</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15079,7 +15079,7 @@
         <v>45210</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>45210</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>46008</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15303,7 +15303,7 @@
         <v>45820</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15376,7 +15376,7 @@
         <v>45560</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15454,7 +15454,7 @@
         <v>45819</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44830</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15600,7 +15600,7 @@
         <v>45821</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>45211</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15746,7 +15746,7 @@
         <v>45875</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15819,7 +15819,7 @@
         <v>45170</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15892,7 +15892,7 @@
         <v>44965</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15965,7 +15965,7 @@
         <v>45827</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>44746</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>44843</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16184,7 +16184,7 @@
         <v>45070</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16257,7 +16257,7 @@
         <v>44847</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>45210</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45535</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16476,7 +16476,7 @@
         <v>44943</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>44943</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44901</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16700,7 +16700,7 @@
         <v>46142</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>44836</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16851,7 +16851,7 @@
         <v>46157</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>46157</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>44994</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17070,7 +17070,7 @@
         <v>45211</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17143,7 +17143,7 @@
         <v>46163</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>46163</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17294,7 +17294,7 @@
         <v>46163</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45832</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17440,7 +17440,7 @@
         <v>45982</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17513,7 +17513,7 @@
         <v>45200</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45393</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17659,7 +17659,7 @@
         <v>46169</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17732,7 +17732,7 @@
         <v>45268</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17805,7 +17805,7 @@
         <v>46171</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17883,7 +17883,7 @@
         <v>46171</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17961,7 +17961,7 @@
         <v>45163</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>46171</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>45412</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18190,7 +18190,7 @@
         <v>45412</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18263,7 +18263,7 @@
         <v>46171</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>45397</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>44620</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18487,7 +18487,7 @@
         <v>45720</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18560,7 +18560,7 @@
         <v>44536</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18638,7 +18638,7 @@
         <v>45873</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18711,7 +18711,7 @@
         <v>46185</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45470</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>44630</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18935,7 +18935,7 @@
         <v>46188</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>45548</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19086,7 +19086,7 @@
         <v>45751</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45330</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19232,7 +19232,7 @@
         <v>45875</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45590</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19383,7 +19383,7 @@
         <v>45217</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19456,7 +19456,7 @@
         <v>46199</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>46199</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>46199</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19675,7 +19675,7 @@
         <v>46205</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19748,7 +19748,7 @@
         <v>46199</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19821,7 +19821,7 @@
         <v>44649</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19894,7 +19894,7 @@
         <v>44629</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>46206</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -20050,7 +20050,7 @@
         <v>44645</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20128,7 +20128,7 @@
         <v>44638</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20201,7 +20201,7 @@
         <v>45200</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20274,7 +20274,7 @@
         <v>45691</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>46253</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45761</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20493,7 +20493,7 @@
         <v>44574</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20566,7 +20566,7 @@
         <v>45210</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20639,7 +20639,7 @@
         <v>45210</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20712,7 +20712,7 @@
         <v>45764</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20785,7 +20785,7 @@
         <v>44900</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>45188</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20936,7 +20936,7 @@
         <v>46261</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -21014,7 +21014,7 @@
         <v>46261</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21092,7 +21092,7 @@
         <v>46262</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21165,7 +21165,7 @@
         <v>46262</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>44746</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21311,7 +21311,7 @@
         <v>44746</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21384,7 +21384,7 @@
         <v>44746</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21457,7 +21457,7 @@
         <v>44797</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21530,7 +21530,7 @@
         <v>45265</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21608,7 +21608,7 @@
         <v>45761</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>44693</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21754,7 +21754,7 @@
         <v>45324</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21827,7 +21827,7 @@
         <v>45211</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21900,7 +21900,7 @@
         <v>45583</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21973,7 +21973,7 @@
         <v>45135</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -22046,7 +22046,7 @@
         <v>45528</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22119,7 +22119,7 @@
         <v>44756</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22192,7 +22192,7 @@
         <v>45201</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22265,7 +22265,7 @@
         <v>46288</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>46288</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22421,7 +22421,7 @@
         <v>46288</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22499,7 +22499,7 @@
         <v>46288</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45268</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22650,7 +22650,7 @@
         <v>46288</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>44973</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22801,7 +22801,7 @@
         <v>46288</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22879,7 +22879,7 @@
         <v>46288</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22957,7 +22957,7 @@
         <v>45590</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -23035,7 +23035,7 @@
         <v>46289</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23113,7 +23113,7 @@
         <v>44496</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23186,7 +23186,7 @@
         <v>44964</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23259,7 +23259,7 @@
         <v>45203</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23332,7 +23332,7 @@
         <v>44572</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>44617</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23488,7 +23488,7 @@
         <v>44930</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23561,7 +23561,7 @@
         <v>46290</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23634,7 +23634,7 @@
         <v>44816</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23707,7 +23707,7 @@
         <v>44937</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23780,7 +23780,7 @@
         <v>45674</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23853,7 +23853,7 @@
         <v>45210</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23926,7 +23926,7 @@
         <v>45114</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23999,7 +23999,7 @@
         <v>45705</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>44917</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45558</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24218,7 +24218,7 @@
         <v>45639</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24291,7 +24291,7 @@
         <v>44622</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>45225</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24437,7 +24437,7 @@
         <v>44616</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45324</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24593,7 +24593,7 @@
         <v>45530</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24666,7 +24666,7 @@
         <v>44536</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24739,7 +24739,7 @@
         <v>45097</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24817,7 +24817,7 @@
         <v>44981</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24890,7 +24890,7 @@
         <v>45329</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24963,7 +24963,7 @@
         <v>45677</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>45201</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25109,7 +25109,7 @@
         <v>44974</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25182,7 +25182,7 @@
         <v>44974</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25255,7 +25255,7 @@
         <v>45211</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25328,7 +25328,7 @@
         <v>44843</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25401,7 +25401,7 @@
         <v>44935</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25474,7 +25474,7 @@
         <v>45371</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25547,7 +25547,7 @@
         <v>45266</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25620,7 +25620,7 @@
         <v>45590</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25698,7 +25698,7 @@
         <v>44890</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25771,7 +25771,7 @@
         <v>45070</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25849,7 +25849,7 @@
         <v>45289</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25927,7 +25927,7 @@
         <v>44942</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -26000,7 +26000,7 @@
         <v>44774</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26073,7 +26073,7 @@
         <v>44756</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26146,7 +26146,7 @@
         <v>45600</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26219,7 +26219,7 @@
         <v>45222</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>44957</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26365,7 +26365,7 @@
         <v>45343</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26438,7 +26438,7 @@
         <v>45722</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26511,7 +26511,7 @@
         <v>45702</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26589,7 +26589,7 @@
         <v>45271</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45524</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45384</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26808,7 +26808,7 @@
         <v>45720</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26881,7 +26881,7 @@
         <v>45684</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26959,7 +26959,7 @@
         <v>45516</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -27032,7 +27032,7 @@
         <v>45545</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27105,7 +27105,7 @@
         <v>45307</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27178,7 +27178,7 @@
         <v>45590</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27251,7 +27251,7 @@
         <v>45790</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27324,7 +27324,7 @@
         <v>45211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27397,7 +27397,7 @@
         <v>44521</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27470,7 +27470,7 @@
         <v>45502</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27543,7 +27543,7 @@
         <v>45716</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27616,7 +27616,7 @@
         <v>45331</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27689,7 +27689,7 @@
         <v>45728</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27767,7 +27767,7 @@
         <v>45616</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27840,7 +27840,7 @@
         <v>45709</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27913,7 +27913,7 @@
         <v>45705</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27986,7 +27986,7 @@
         <v>45618</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28064,7 +28064,7 @@
         <v>45757</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>46064</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>

--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>44581</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>44610</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44484</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>46009</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45097</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>45203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>44880</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>45330</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>44628</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>45441</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45015</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45201</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44546</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45435</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45716</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45947</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45821</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45821</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45035</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45989</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>45705</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>44972</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>45181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45015</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45162</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>45761</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>45112</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45797</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45821</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>45703</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45703</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>44619</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>44574</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44746</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>44840</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>44852</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>44473</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44539</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>44523</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>44614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44766</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44880</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44496</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>44758</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44693</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44649</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44571</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44880</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>44523</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44592</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44530</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>45674</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44630</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>45590</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44843</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45677</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44830</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44574</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>45397</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45705</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44629</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45590</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44830</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>45590</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45324</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>46003</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>45545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>44521</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45705</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45470</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>46008</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>45616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45211</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45097</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45600</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45728</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45502</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44521</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>44847</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45709</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>45210</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45210</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>46029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>46029</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45790</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45897</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45716</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44942</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44746</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44693</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>44971</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45909</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>46042</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44993</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45240</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>44797</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45331</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45911</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45610</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45798</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45798</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45798</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45163</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45343</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>46050</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>46051</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45268</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45804</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>45804</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>45804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45754</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45373</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>46057</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>45265</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>46061</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>45560</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44746</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44746</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44536</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>46071</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>46071</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>45393</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>46071</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44901</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>46077</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>45720</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>45947</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>46080</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44883</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45958</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45958</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45744</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45958</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>45199</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45817</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45965</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>45548</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>45966</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44964</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>45201</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>44774</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>46100</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>44937</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>45764</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45818</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>44994</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45819</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44645</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45821</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45820</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>45820</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44836</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>46119</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45722</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>45222</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45827</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>44843</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>44865</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44638</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45443</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>44936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>44812</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>45201</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>45203</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>44986</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>44620</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>45211</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45170</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>45832</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>45211</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45266</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>45167</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44974</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44974</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45070</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45131</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45664</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44994</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>45033</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45558</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45210</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45210</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>44943</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45875</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45560</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>45343</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44943</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45135</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>44935</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45384</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>44965</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45006</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45225</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>45188</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45329</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45873</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>44739</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45761</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45324</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>44756</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45875</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>44936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45639</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>46157</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>46157</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45535</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45243</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45412</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45412</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>46142</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45544</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>46163</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>46163</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45271</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45268</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45530</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>46163</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>44572</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44903</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45982</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>46169</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>46171</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>46171</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>45271</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>46171</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>46171</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>44986</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45217</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>44930</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45887</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45887</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45887</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45330</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45015</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>46185</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>46188</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>44876</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44900</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44812</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44957</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45371</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44622</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45516</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>45271</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45268</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45210</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>46205</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>46199</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>46199</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45350</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46199</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>46199</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46206</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45210</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>44993</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>46261</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>46261</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45702</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>46262</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>46262</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>44890</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45761</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>44973</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44614</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44816</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>45583</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>44943</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>44981</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>44756</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45412</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45412</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44965</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>44496</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45200</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>45590</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45709</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45211</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>45114</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>44489</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>46288</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45289</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>46288</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>46289</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46288</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45548</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>46288</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>46288</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>46288</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>46288</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>45211</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44881</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>46290</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>45460</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45524</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>46293</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>44553</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>45590</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>44649</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44617</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45097</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45706</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>45722</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>44616</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46253</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45590</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45070</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45751</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44999</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45200</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45528</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45210</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44848</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>45260</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45393</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>45516</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>44746</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>45516</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>45674</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>44917</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45691</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45265</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45211</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45720</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45299</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>45720</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45684</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45307</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45618</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45757</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>46064</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>

--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>44473</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>45708</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1303,7 +1303,7 @@
         <v>44648</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
         <v>44581</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1521,7 +1521,7 @@
         <v>44610</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1631,7 +1631,7 @@
         <v>44484</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>46009</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>45097</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>45203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2060,7 +2060,7 @@
         <v>44524</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2171,7 +2171,7 @@
         <v>44880</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>45330</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2383,7 +2383,7 @@
         <v>44628</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2493,7 +2493,7 @@
         <v>45215</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>45441</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2714,7 +2714,7 @@
         <v>45015</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
         <v>45201</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2934,7 +2934,7 @@
         <v>44546</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3039,7 +3039,7 @@
         <v>45435</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>45716</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>45947</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3364,7 +3364,7 @@
         <v>45821</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>45821</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3584,7 +3584,7 @@
         <v>45035</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3689,7 +3689,7 @@
         <v>45989</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3794,7 +3794,7 @@
         <v>45705</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3899,7 +3899,7 @@
         <v>44972</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4004,7 +4004,7 @@
         <v>45181</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4109,7 +4109,7 @@
         <v>45015</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>45162</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>45761</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4433,7 +4433,7 @@
         <v>45210</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4538,7 +4538,7 @@
         <v>45112</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>45797</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>45821</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>45703</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5083,7 +5083,7 @@
         <v>45703</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>44619</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
         <v>44574</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5339,7 +5339,7 @@
         <v>44746</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5412,7 +5412,7 @@
         <v>44840</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5485,7 +5485,7 @@
         <v>44852</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5558,7 +5558,7 @@
         <v>44473</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5631,7 +5631,7 @@
         <v>44539</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5704,7 +5704,7 @@
         <v>44523</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>44614</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5855,7 +5855,7 @@
         <v>44766</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5928,7 +5928,7 @@
         <v>44880</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6001,7 +6001,7 @@
         <v>44496</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         <v>44758</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6152,7 +6152,7 @@
         <v>44693</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6225,7 +6225,7 @@
         <v>44649</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6298,7 +6298,7 @@
         <v>44571</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6371,7 +6371,7 @@
         <v>44880</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6444,7 +6444,7 @@
         <v>44526</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6522,7 +6522,7 @@
         <v>44523</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>44592</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6668,7 +6668,7 @@
         <v>44530</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>45674</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44630</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>45590</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6965,7 +6965,7 @@
         <v>44843</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7038,7 +7038,7 @@
         <v>45677</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>44830</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7184,7 +7184,7 @@
         <v>44574</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7257,7 +7257,7 @@
         <v>45397</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45705</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7403,7 +7403,7 @@
         <v>44629</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45590</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7554,7 +7554,7 @@
         <v>44830</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7627,7 +7627,7 @@
         <v>45516</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>45590</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
         <v>45324</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7846,7 +7846,7 @@
         <v>46003</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7919,7 +7919,7 @@
         <v>45545</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7992,7 +7992,7 @@
         <v>45887</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8070,7 +8070,7 @@
         <v>44521</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8143,7 +8143,7 @@
         <v>45705</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8216,7 +8216,7 @@
         <v>45470</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8294,7 +8294,7 @@
         <v>46008</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>45616</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8445,7 +8445,7 @@
         <v>45211</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8518,7 +8518,7 @@
         <v>45097</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>45600</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45728</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8742,7 +8742,7 @@
         <v>45502</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8815,7 +8815,7 @@
         <v>44521</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>44847</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8961,7 +8961,7 @@
         <v>45709</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9034,7 +9034,7 @@
         <v>45210</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9107,7 +9107,7 @@
         <v>45210</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>46029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9258,7 +9258,7 @@
         <v>46029</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9336,7 +9336,7 @@
         <v>45790</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9409,7 +9409,7 @@
         <v>45897</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9482,7 +9482,7 @@
         <v>45716</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9555,7 +9555,7 @@
         <v>44942</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44746</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>44536</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9774,7 +9774,7 @@
         <v>44693</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9847,7 +9847,7 @@
         <v>44971</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>45909</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9993,7 +9993,7 @@
         <v>46042</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10066,7 +10066,7 @@
         <v>44993</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>45909</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10217,7 +10217,7 @@
         <v>45240</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10290,7 +10290,7 @@
         <v>44797</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10363,7 +10363,7 @@
         <v>45331</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10436,7 +10436,7 @@
         <v>45911</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10509,7 +10509,7 @@
         <v>45610</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10582,7 +10582,7 @@
         <v>45600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>45798</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>45798</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10811,7 +10811,7 @@
         <v>45798</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>45163</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>45343</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>46050</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11113,7 +11113,7 @@
         <v>46051</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>45268</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11264,7 +11264,7 @@
         <v>45804</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>45804</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
         <v>45804</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>45754</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>45373</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>46057</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>45265</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11790,7 +11790,7 @@
         <v>46061</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11863,7 +11863,7 @@
         <v>45560</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11941,7 +11941,7 @@
         <v>44746</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44746</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>44536</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>46071</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>46071</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12311,7 +12311,7 @@
         <v>45393</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12384,7 +12384,7 @@
         <v>46071</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12457,7 +12457,7 @@
         <v>44901</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12535,7 +12535,7 @@
         <v>46077</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>45720</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12681,7 +12681,7 @@
         <v>45947</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12754,7 +12754,7 @@
         <v>46080</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44883</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12905,7 +12905,7 @@
         <v>45958</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>45958</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
         <v>45744</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13124,7 +13124,7 @@
         <v>45958</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>45199</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13270,7 +13270,7 @@
         <v>44958</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13343,7 +13343,7 @@
         <v>45817</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13416,7 +13416,7 @@
         <v>45965</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13489,7 +13489,7 @@
         <v>45548</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13562,7 +13562,7 @@
         <v>45966</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44964</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13708,7 +13708,7 @@
         <v>45201</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13781,7 +13781,7 @@
         <v>44774</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13854,7 +13854,7 @@
         <v>46100</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13927,7 +13927,7 @@
         <v>44937</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -14000,7 +14000,7 @@
         <v>45764</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14073,7 +14073,7 @@
         <v>45818</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14146,7 +14146,7 @@
         <v>44994</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>45819</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14292,7 +14292,7 @@
         <v>44645</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14370,7 +14370,7 @@
         <v>45821</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>45820</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14516,7 +14516,7 @@
         <v>45820</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14589,7 +14589,7 @@
         <v>44836</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>46119</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14735,7 +14735,7 @@
         <v>45722</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>45222</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>45827</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14954,7 +14954,7 @@
         <v>44843</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15027,7 +15027,7 @@
         <v>44865</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15100,7 +15100,7 @@
         <v>44638</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15173,7 +15173,7 @@
         <v>45443</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>44936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15319,7 +15319,7 @@
         <v>44812</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>45201</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>45203</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>44986</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>44620</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>45211</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>45170</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>45832</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>45211</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>45266</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>45167</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44974</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>44974</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>45070</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>45131</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>45664</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16492,7 +16492,7 @@
         <v>44994</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>45033</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16638,7 +16638,7 @@
         <v>45558</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45210</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16784,7 +16784,7 @@
         <v>45210</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         <v>44943</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16930,7 +16930,7 @@
         <v>45875</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17003,7 +17003,7 @@
         <v>45560</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>45343</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17154,7 +17154,7 @@
         <v>44943</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17227,7 +17227,7 @@
         <v>45135</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17300,7 +17300,7 @@
         <v>45728</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17378,7 +17378,7 @@
         <v>44935</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17451,7 +17451,7 @@
         <v>45384</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17524,7 +17524,7 @@
         <v>44965</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>45006</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>45225</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>45188</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17821,7 +17821,7 @@
         <v>45329</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45873</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17967,7 +17967,7 @@
         <v>44739</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18045,7 +18045,7 @@
         <v>45761</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45324</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18196,7 +18196,7 @@
         <v>44756</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18269,7 +18269,7 @@
         <v>45875</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18347,7 +18347,7 @@
         <v>44936</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18420,7 +18420,7 @@
         <v>45639</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>46157</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18566,7 +18566,7 @@
         <v>46157</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18639,7 +18639,7 @@
         <v>45535</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18712,7 +18712,7 @@
         <v>45243</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18785,7 +18785,7 @@
         <v>45412</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18858,7 +18858,7 @@
         <v>45412</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>46142</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19009,7 +19009,7 @@
         <v>45544</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>46163</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>46163</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19228,7 +19228,7 @@
         <v>45271</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45268</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19374,7 +19374,7 @@
         <v>45530</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19447,7 +19447,7 @@
         <v>46163</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>44572</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>44903</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45982</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>46169</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>46171</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>46171</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>45271</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20051,7 +20051,7 @@
         <v>46171</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>46171</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20207,7 +20207,7 @@
         <v>44986</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>45217</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>44930</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>45887</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20504,7 +20504,7 @@
         <v>45887</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20582,7 +20582,7 @@
         <v>45887</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20660,7 +20660,7 @@
         <v>45330</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>45015</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20806,7 +20806,7 @@
         <v>46185</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20879,7 +20879,7 @@
         <v>46188</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>44876</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>44900</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21108,7 +21108,7 @@
         <v>44812</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44957</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21254,7 +21254,7 @@
         <v>45371</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21327,7 +21327,7 @@
         <v>44622</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21400,7 +21400,7 @@
         <v>45516</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21473,7 +21473,7 @@
         <v>45271</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21546,7 +21546,7 @@
         <v>45268</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45210</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>46205</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>46199</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21838,7 +21838,7 @@
         <v>46199</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45350</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21984,7 +21984,7 @@
         <v>46199</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22057,7 +22057,7 @@
         <v>46199</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22130,7 +22130,7 @@
         <v>46206</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22208,7 +22208,7 @@
         <v>45210</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22281,7 +22281,7 @@
         <v>44993</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22354,7 +22354,7 @@
         <v>46261</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>46261</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22510,7 +22510,7 @@
         <v>45702</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22588,7 +22588,7 @@
         <v>46262</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22661,7 +22661,7 @@
         <v>46262</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22734,7 +22734,7 @@
         <v>44890</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22807,7 +22807,7 @@
         <v>45761</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22880,7 +22880,7 @@
         <v>44973</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22953,7 +22953,7 @@
         <v>44614</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23031,7 +23031,7 @@
         <v>44816</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23104,7 +23104,7 @@
         <v>45583</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>44943</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23250,7 +23250,7 @@
         <v>44981</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23323,7 +23323,7 @@
         <v>45210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23396,7 +23396,7 @@
         <v>44756</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45412</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23542,7 +23542,7 @@
         <v>45412</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44965</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23688,7 +23688,7 @@
         <v>44496</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23761,7 +23761,7 @@
         <v>45200</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23834,7 +23834,7 @@
         <v>45590</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23912,7 +23912,7 @@
         <v>45709</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23985,7 +23985,7 @@
         <v>45211</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24058,7 +24058,7 @@
         <v>45114</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24131,7 +24131,7 @@
         <v>44489</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24209,7 +24209,7 @@
         <v>46288</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45289</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24365,7 +24365,7 @@
         <v>46288</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24443,7 +24443,7 @@
         <v>46289</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24521,7 +24521,7 @@
         <v>46288</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45548</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>46288</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24750,7 +24750,7 @@
         <v>46288</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>46288</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24906,7 +24906,7 @@
         <v>46288</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24984,7 +24984,7 @@
         <v>45211</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -25057,7 +25057,7 @@
         <v>44881</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>46290</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25203,7 +25203,7 @@
         <v>45460</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25276,7 +25276,7 @@
         <v>45524</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25349,7 +25349,7 @@
         <v>46293</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25422,7 +25422,7 @@
         <v>44553</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25495,7 +25495,7 @@
         <v>45590</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>44649</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>44617</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25724,7 +25724,7 @@
         <v>45097</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25802,7 +25802,7 @@
         <v>45706</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25875,7 +25875,7 @@
         <v>45722</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25948,7 +25948,7 @@
         <v>44616</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -26026,7 +26026,7 @@
         <v>46253</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45590</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26177,7 +26177,7 @@
         <v>45070</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26250,7 +26250,7 @@
         <v>45751</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26323,7 +26323,7 @@
         <v>44999</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26396,7 +26396,7 @@
         <v>45200</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45528</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26542,7 +26542,7 @@
         <v>45210</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26615,7 +26615,7 @@
         <v>44848</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26688,7 +26688,7 @@
         <v>45260</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26761,7 +26761,7 @@
         <v>45393</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>45516</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26907,7 +26907,7 @@
         <v>44746</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26980,7 +26980,7 @@
         <v>45516</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27053,7 +27053,7 @@
         <v>45674</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27126,7 +27126,7 @@
         <v>44917</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27199,7 +27199,7 @@
         <v>45691</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45265</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27350,7 +27350,7 @@
         <v>45211</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45720</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45299</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27569,7 +27569,7 @@
         <v>45720</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27642,7 +27642,7 @@
         <v>45684</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45307</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45618</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27871,7 +27871,7 @@
         <v>45757</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27949,7 +27949,7 @@
         <v>46064</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>

--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45708</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44648</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>44581</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44610</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45441</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45215</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44484</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45330</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45201</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45015</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>44524</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>44880</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>46009</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45097</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44628</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44546</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45181</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>45210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>45716</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45705</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>45162</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>45821</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>45821</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45947</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45761</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45989</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>45015</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45035</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45435</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>45797</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45821</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>45703</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45703</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44619</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44574</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>44746</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>44840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44539</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>44766</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>44880</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44496</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44758</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44571</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44693</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44526</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44880</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>44592</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45412</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45412</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45097</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44943</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45097</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44848</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45709</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44901</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44981</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45329</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>44836</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45677</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45201</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44974</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>44974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44994</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44812</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45393</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45211</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>45460</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44883</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45343</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45211</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>45210</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45211</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44553</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>45131</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45299</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>45200</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44843</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>44935</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45371</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45393</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>44812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45590</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>44890</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45516</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45070</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45289</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44942</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>45443</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>45265</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>45271</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>45268</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>45271</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>44774</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>44489</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>44756</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45887</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45887</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>45163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45887</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45887</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45222</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45412</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45412</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>44957</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45397</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44521</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45897</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45343</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45722</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45243</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45702</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45271</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45524</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>44903</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45384</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45909</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44620</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45909</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45720</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>45590</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45674</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45720</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45911</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>44536</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45684</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45516</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>45545</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45470</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>45260</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44630</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45516</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45516</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44999</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45307</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45590</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45790</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45548</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45751</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45330</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45211</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>44521</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45502</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44994</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45033</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45716</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45331</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45728</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45616</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45709</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45240</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>45705</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44865</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45590</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45560</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45600</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44936</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45610</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44876</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45798</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45798</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45798</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45590</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45217</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45210</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45744</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45548</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>44936</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>44649</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45804</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>44629</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45804</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45804</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45199</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>44645</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44943</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44638</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44739</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45200</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45754</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44993</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45691</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45720</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45350</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>44830</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45947</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45817</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45015</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45818</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45761</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45820</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45820</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44574</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45819</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45821</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44971</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44614</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45210</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45210</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44958</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>44965</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45827</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45006</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45764</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44900</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45958</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45958</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45958</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45706</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>44986</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45188</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44993</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>44881</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45966</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44746</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45832</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45664</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45722</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>44746</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>44746</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44986</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>44797</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45265</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45761</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>44693</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45544</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45324</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45210</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45210</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45873</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45211</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>44830</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45875</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45211</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>45583</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45135</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45528</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>44756</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>46100</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45201</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>44746</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44843</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>45070</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>44847</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45210</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45535</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44943</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>46119</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45268</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>44973</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>46003</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>46008</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45590</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>44496</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44964</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45203</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45728</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44572</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44617</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>44930</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44816</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>46029</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>46029</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>45167</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>44937</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45674</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45560</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45210</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45114</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45705</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>46042</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44917</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45558</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45639</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>44622</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45225</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44616</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45324</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>45875</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45170</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>45530</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44965</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46050</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44536</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>46051</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>46057</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>46061</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>46071</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>46071</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>46071</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>46077</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>46080</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>46142</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>46157</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>46157</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>46163</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46163</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>46163</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45982</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>46169</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>46171</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>46171</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>46171</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>46171</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46185</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>46188</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>46199</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>46199</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>46199</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>46205</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>46199</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>46206</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>46288</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>46288</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>46288</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>46288</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>46288</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>46288</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>46288</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>46289</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>46290</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>46293</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>46253</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>46300</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>46300</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>46300</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>46300</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>46300</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>46261</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>46262</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>46262</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>46261</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45618</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45757</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>46064</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>

--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45708</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44648</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>44581</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44610</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45441</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1629,7 +1629,7 @@
         <v>45215</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1739,7 +1739,7 @@
         <v>44484</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45330</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1951,7 +1951,7 @@
         <v>45203</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45201</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2167,7 +2167,7 @@
         <v>45015</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2277,7 +2277,7 @@
         <v>44524</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2388,7 +2388,7 @@
         <v>44880</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2494,7 +2494,7 @@
         <v>46009</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45097</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>44628</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46300</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>44546</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3032,7 +3032,7 @@
         <v>45181</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3137,7 +3137,7 @@
         <v>45210</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>45716</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3352,7 +3352,7 @@
         <v>45705</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3457,7 +3457,7 @@
         <v>45162</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         <v>45821</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3677,7 +3677,7 @@
         <v>45821</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45947</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3892,7 +3892,7 @@
         <v>45761</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3997,7 +3997,7 @@
         <v>45989</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4102,7 +4102,7 @@
         <v>44972</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45112</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4317,7 +4317,7 @@
         <v>45015</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4426,7 +4426,7 @@
         <v>45035</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4531,7 +4531,7 @@
         <v>45435</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4641,7 +4641,7 @@
         <v>45716</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4746,7 +4746,7 @@
         <v>45797</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4856,7 +4856,7 @@
         <v>45821</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4966,7 +4966,7 @@
         <v>45703</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>45703</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5186,7 +5186,7 @@
         <v>44619</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5259,7 +5259,7 @@
         <v>44574</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5332,7 +5332,7 @@
         <v>44746</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5405,7 +5405,7 @@
         <v>44852</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>44840</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5551,7 +5551,7 @@
         <v>44539</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5624,7 +5624,7 @@
         <v>44523</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5697,7 +5697,7 @@
         <v>44614</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>44766</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5848,7 +5848,7 @@
         <v>44880</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44496</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6072,7 +6072,7 @@
         <v>44523</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6145,7 +6145,7 @@
         <v>44758</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6218,7 +6218,7 @@
         <v>44571</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>44693</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6364,7 +6364,7 @@
         <v>44526</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>44880</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6515,7 +6515,7 @@
         <v>44592</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6588,7 +6588,7 @@
         <v>45412</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
         <v>45412</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>44530</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6807,7 +6807,7 @@
         <v>45097</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6880,7 +6880,7 @@
         <v>44943</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6953,7 +6953,7 @@
         <v>45097</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -7031,7 +7031,7 @@
         <v>44848</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7104,7 +7104,7 @@
         <v>45709</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7177,7 +7177,7 @@
         <v>44901</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>45373</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44981</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7401,7 +7401,7 @@
         <v>45329</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7474,7 +7474,7 @@
         <v>44836</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45677</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7620,7 +7620,7 @@
         <v>45201</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44974</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>44974</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7839,7 +7839,7 @@
         <v>44994</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44812</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45393</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8058,7 +8058,7 @@
         <v>45211</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8131,7 +8131,7 @@
         <v>45460</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44883</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8282,7 +8282,7 @@
         <v>45343</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8355,7 +8355,7 @@
         <v>45211</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8428,7 +8428,7 @@
         <v>45210</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8501,7 +8501,7 @@
         <v>45211</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>44553</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8647,7 +8647,7 @@
         <v>45131</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45299</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8793,7 +8793,7 @@
         <v>45200</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
         <v>44843</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8939,7 +8939,7 @@
         <v>44935</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>45371</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45393</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>45266</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9231,7 +9231,7 @@
         <v>44812</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9304,7 +9304,7 @@
         <v>45590</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>44890</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>45516</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9528,7 +9528,7 @@
         <v>45070</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>45289</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44942</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9757,7 +9757,7 @@
         <v>45443</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>45265</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>45271</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9981,7 +9981,7 @@
         <v>45268</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10054,7 +10054,7 @@
         <v>45268</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10127,7 +10127,7 @@
         <v>45271</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>44774</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>44489</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10351,7 +10351,7 @@
         <v>44756</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10424,7 +10424,7 @@
         <v>45887</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>45887</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10580,7 +10580,7 @@
         <v>45600</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>45163</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45887</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45887</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45222</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10960,7 +10960,7 @@
         <v>45412</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>45412</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11106,7 +11106,7 @@
         <v>44957</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11179,7 +11179,7 @@
         <v>45397</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11252,7 +11252,7 @@
         <v>44521</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45897</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45343</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>45722</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45243</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>45702</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11695,7 +11695,7 @@
         <v>45271</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11768,7 +11768,7 @@
         <v>45524</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>44903</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>45384</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11987,7 +11987,7 @@
         <v>45909</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12060,7 +12060,7 @@
         <v>44620</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12133,7 +12133,7 @@
         <v>45909</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12206,7 +12206,7 @@
         <v>45720</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>45590</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>45674</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>45720</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12503,7 +12503,7 @@
         <v>45911</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12576,7 +12576,7 @@
         <v>44536</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12654,7 +12654,7 @@
         <v>45684</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>45516</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12805,7 +12805,7 @@
         <v>45545</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12878,7 +12878,7 @@
         <v>45470</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12956,7 +12956,7 @@
         <v>45260</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -13029,7 +13029,7 @@
         <v>44630</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>45516</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>45516</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13248,7 +13248,7 @@
         <v>44999</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
         <v>45307</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45590</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45790</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>45548</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13613,7 +13613,7 @@
         <v>45751</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13686,7 +13686,7 @@
         <v>45330</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>45211</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13832,7 +13832,7 @@
         <v>44521</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>45502</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13978,7 +13978,7 @@
         <v>44994</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14051,7 +14051,7 @@
         <v>45033</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14124,7 +14124,7 @@
         <v>45716</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>45331</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>45728</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14348,7 +14348,7 @@
         <v>45616</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>45709</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14494,7 +14494,7 @@
         <v>45240</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>45705</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14640,7 +14640,7 @@
         <v>44865</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>45590</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14786,7 +14786,7 @@
         <v>45560</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14864,7 +14864,7 @@
         <v>45600</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14937,7 +14937,7 @@
         <v>44936</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45610</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15083,7 +15083,7 @@
         <v>44876</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>45798</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15239,7 +15239,7 @@
         <v>45798</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>45798</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45590</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15473,7 +15473,7 @@
         <v>45217</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15546,7 +15546,7 @@
         <v>45210</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15619,7 +15619,7 @@
         <v>45744</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>45548</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>44936</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15838,7 +15838,7 @@
         <v>44649</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15911,7 +15911,7 @@
         <v>45804</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>44629</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16067,7 +16067,7 @@
         <v>45804</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45804</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>45199</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16286,7 +16286,7 @@
         <v>44645</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>44943</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>44638</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44739</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45200</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45754</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44993</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>45691</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>45720</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16958,7 +16958,7 @@
         <v>45350</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17031,7 +17031,7 @@
         <v>44830</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17104,7 +17104,7 @@
         <v>45947</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>45817</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17250,7 +17250,7 @@
         <v>45015</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17323,7 +17323,7 @@
         <v>45818</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17396,7 +17396,7 @@
         <v>45761</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17469,7 +17469,7 @@
         <v>45820</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45820</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17615,7 +17615,7 @@
         <v>44574</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17688,7 +17688,7 @@
         <v>45819</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17761,7 +17761,7 @@
         <v>45821</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>44971</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>44614</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17985,7 +17985,7 @@
         <v>45210</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18058,7 +18058,7 @@
         <v>45210</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44958</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>44965</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18277,7 +18277,7 @@
         <v>45827</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18350,7 +18350,7 @@
         <v>45006</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18423,7 +18423,7 @@
         <v>45764</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18496,7 +18496,7 @@
         <v>44900</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18569,7 +18569,7 @@
         <v>45958</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18642,7 +18642,7 @@
         <v>45958</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18715,7 +18715,7 @@
         <v>45958</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45706</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18861,7 +18861,7 @@
         <v>44986</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18934,7 +18934,7 @@
         <v>45188</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -19012,7 +19012,7 @@
         <v>44993</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>44881</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45966</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19231,7 +19231,7 @@
         <v>45965</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19304,7 +19304,7 @@
         <v>44746</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19377,7 +19377,7 @@
         <v>45832</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45664</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>45722</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>44746</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>44746</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>44986</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19815,7 +19815,7 @@
         <v>44797</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>45265</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19966,7 +19966,7 @@
         <v>45761</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20039,7 +20039,7 @@
         <v>44693</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>45544</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20185,7 +20185,7 @@
         <v>45324</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20258,7 +20258,7 @@
         <v>45210</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20331,7 +20331,7 @@
         <v>45210</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45873</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>45211</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>44830</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45875</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45211</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>45583</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>45135</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45528</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>44756</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>46100</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45201</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>44746</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>44843</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21358,7 +21358,7 @@
         <v>45070</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21431,7 +21431,7 @@
         <v>44847</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21504,7 +21504,7 @@
         <v>45210</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21577,7 +21577,7 @@
         <v>45535</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44943</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>46119</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45268</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21869,7 +21869,7 @@
         <v>44973</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21942,7 +21942,7 @@
         <v>46003</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22015,7 +22015,7 @@
         <v>46008</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22093,7 +22093,7 @@
         <v>45590</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>44496</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>44964</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45203</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>45728</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22468,7 +22468,7 @@
         <v>44572</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44617</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22624,7 +22624,7 @@
         <v>44930</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>44816</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22770,7 +22770,7 @@
         <v>46029</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22848,7 +22848,7 @@
         <v>46029</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22926,7 +22926,7 @@
         <v>45167</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>44937</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23072,7 +23072,7 @@
         <v>45674</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23145,7 +23145,7 @@
         <v>45560</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45210</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45114</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45705</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>46042</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>44917</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>45558</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45639</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>44622</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>45225</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>44616</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45324</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24036,7 +24036,7 @@
         <v>45875</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24109,7 +24109,7 @@
         <v>45170</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24182,7 +24182,7 @@
         <v>45530</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24255,7 +24255,7 @@
         <v>44965</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24328,7 +24328,7 @@
         <v>46050</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44536</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24474,7 +24474,7 @@
         <v>46051</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24552,7 +24552,7 @@
         <v>46057</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24630,7 +24630,7 @@
         <v>46061</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24703,7 +24703,7 @@
         <v>46071</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24776,7 +24776,7 @@
         <v>46071</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24849,7 +24849,7 @@
         <v>46071</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24922,7 +24922,7 @@
         <v>46077</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24995,7 +24995,7 @@
         <v>46080</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25068,7 +25068,7 @@
         <v>46142</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25146,7 +25146,7 @@
         <v>46157</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25219,7 +25219,7 @@
         <v>46157</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25292,7 +25292,7 @@
         <v>46163</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25370,7 +25370,7 @@
         <v>46163</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25443,7 +25443,7 @@
         <v>46163</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25516,7 +25516,7 @@
         <v>45982</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>46169</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25662,7 +25662,7 @@
         <v>46171</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>46171</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25818,7 +25818,7 @@
         <v>46171</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25896,7 +25896,7 @@
         <v>46171</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>46185</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26047,7 +26047,7 @@
         <v>46188</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26125,7 +26125,7 @@
         <v>46199</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26198,7 +26198,7 @@
         <v>46199</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26271,7 +26271,7 @@
         <v>46199</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>46205</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>46199</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>46206</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26568,7 +26568,7 @@
         <v>46288</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26646,7 +26646,7 @@
         <v>46288</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26724,7 +26724,7 @@
         <v>46288</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26802,7 +26802,7 @@
         <v>46288</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26880,7 +26880,7 @@
         <v>46288</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26958,7 +26958,7 @@
         <v>46288</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -27036,7 +27036,7 @@
         <v>46288</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27114,7 +27114,7 @@
         <v>46289</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>46290</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27265,7 +27265,7 @@
         <v>46293</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>46253</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>46300</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27484,7 +27484,7 @@
         <v>46300</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>46300</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27630,7 +27630,7 @@
         <v>46300</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>46300</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27776,7 +27776,7 @@
         <v>46261</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27854,7 +27854,7 @@
         <v>46262</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27927,7 +27927,7 @@
         <v>46262</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -28000,7 +28000,7 @@
         <v>46261</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28078,7 +28078,7 @@
         <v>45618</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -28156,7 +28156,7 @@
         <v>45757</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -28234,7 +28234,7 @@
         <v>46064</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>

--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45708</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44648</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>44581</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44610</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45097</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45203</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>44524</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>46009</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>45330</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44628</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45441</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45015</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45201</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>46300</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44546</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>45435</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45035</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>45705</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45947</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45015</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>45162</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>45761</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45210</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>45716</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>45821</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>45821</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45716</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45821</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45703</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45703</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44619</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44746</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44539</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>44523</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44766</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44880</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44496</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44758</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>44693</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44880</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>44526</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>44523</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>44592</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>45674</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44630</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45590</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44843</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>45677</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>44830</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>44574</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>45397</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>45705</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44629</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>45590</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44830</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45470</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>45324</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>44847</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45097</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45600</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>44521</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>45210</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44942</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44693</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44536</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45240</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44971</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44797</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44993</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>45268</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>45163</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>45343</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>45373</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>45265</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>45560</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>45393</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44746</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44746</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44901</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44883</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45744</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>45199</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44958</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44964</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>45548</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45201</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>44774</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45764</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>44994</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>44937</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44645</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>45170</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45887</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>44836</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45722</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>45167</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>45222</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>44843</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>44865</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>45887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>45887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45887</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44638</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45897</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45443</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45875</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44936</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45560</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44812</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45728</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45201</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45203</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44965</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44986</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45909</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45909</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45911</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44620</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45211</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45211</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45266</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44974</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>44974</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45070</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45131</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45664</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>44994</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45033</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45558</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45210</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45210</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44943</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45343</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45947</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44943</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>45135</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44935</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>46157</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45958</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45384</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>46157</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45958</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45958</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>46142</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45965</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45966</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45006</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45225</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>45188</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>45329</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>46163</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>46163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>46163</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44739</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45761</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45324</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>44756</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>44936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45639</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45535</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>45243</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>45412</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45412</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45544</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>45982</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>45271</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45268</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45530</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>46169</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>44572</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>44903</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>46003</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>46171</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>46171</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>46171</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45271</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>46008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>44986</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45217</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>46171</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>44930</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45330</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>46029</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>46029</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45015</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44876</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44900</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>46042</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44812</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44957</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45371</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>46050</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>46051</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44622</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>46057</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46061</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45516</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46185</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>46188</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45271</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>46071</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>46071</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>46071</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45210</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>46077</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>46080</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45350</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45210</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>46100</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44993</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45702</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44890</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>46119</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>44973</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44614</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44816</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45583</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44943</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44981</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45210</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>44756</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45412</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45412</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>46205</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>46199</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>46199</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>44965</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>44496</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45200</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45590</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>46199</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45709</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>46199</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>46206</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45211</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45114</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44489</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45289</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45548</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45211</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44881</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45460</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45524</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44553</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45590</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>44649</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44617</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45097</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45706</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45722</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44616</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45590</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45070</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45751</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44999</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45200</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45528</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45210</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>46288</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>46288</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>46289</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>46288</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44848</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>46288</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>46288</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>46288</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>46288</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45260</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45393</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>46290</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45516</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44746</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>46293</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>45516</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45674</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>44917</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45691</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45265</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46253</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45211</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45720</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45299</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46300</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45720</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>46300</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>46300</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45684</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>46300</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>46300</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45307</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>45516</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>45590</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45545</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>44521</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>45705</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45616</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45211</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45728</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45502</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45709</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45790</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45716</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>46261</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45331</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45610</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>46261</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45600</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>45798</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45798</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>46262</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>46262</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>45798</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45804</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>45804</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45804</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>45754</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45817</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45818</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45821</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45820</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45820</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45827</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45832</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45873</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45875</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45618</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45757</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>46064</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>

--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45708</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44648</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>44581</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44610</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45097</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
         <v>45203</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1730,7 +1730,7 @@
         <v>44524</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1841,7 +1841,7 @@
         <v>44880</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1947,7 +1947,7 @@
         <v>46009</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         <v>45330</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2164,7 +2164,7 @@
         <v>44628</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2274,7 +2274,7 @@
         <v>45215</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>45441</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2495,7 +2495,7 @@
         <v>45015</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45201</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2715,7 +2715,7 @@
         <v>46300</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44546</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>45435</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45035</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>45705</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3246,7 +3246,7 @@
         <v>44972</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3351,7 +3351,7 @@
         <v>45181</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3456,7 +3456,7 @@
         <v>45947</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>45015</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>45162</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>45761</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45210</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -3990,7 +3990,7 @@
         <v>45112</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
         <v>45716</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>45821</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>45821</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45716</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45821</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45703</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45703</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44619</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44746</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44539</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>44523</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44766</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44880</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44496</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44758</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>44693</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44880</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>44526</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>44523</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>44592</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>44530</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>45674</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6523,7 +6523,7 @@
         <v>44630</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6596,7 +6596,7 @@
         <v>45590</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>44843</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6747,7 +6747,7 @@
         <v>45677</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6820,7 +6820,7 @@
         <v>44830</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6893,7 +6893,7 @@
         <v>44574</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6966,7 +6966,7 @@
         <v>45397</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7039,7 +7039,7 @@
         <v>45705</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>44629</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7190,7 +7190,7 @@
         <v>45590</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7263,7 +7263,7 @@
         <v>44830</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
         <v>45470</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7414,7 +7414,7 @@
         <v>45324</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7487,7 +7487,7 @@
         <v>44847</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7560,7 +7560,7 @@
         <v>45097</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         <v>45600</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7706,7 +7706,7 @@
         <v>44521</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7779,7 +7779,7 @@
         <v>45210</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>45210</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>44942</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44693</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8071,7 +8071,7 @@
         <v>44746</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>44536</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8217,7 +8217,7 @@
         <v>45240</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8290,7 +8290,7 @@
         <v>44971</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8363,7 +8363,7 @@
         <v>44797</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8436,7 +8436,7 @@
         <v>44993</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8514,7 +8514,7 @@
         <v>45268</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8587,7 +8587,7 @@
         <v>45163</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8665,7 +8665,7 @@
         <v>45343</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>45373</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>45265</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8889,7 +8889,7 @@
         <v>44536</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8967,7 +8967,7 @@
         <v>45560</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>45393</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>44746</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44746</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>44901</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44883</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>45744</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>45199</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9566,7 +9566,7 @@
         <v>44958</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9639,7 +9639,7 @@
         <v>44964</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9712,7 +9712,7 @@
         <v>45548</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>45201</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9858,7 +9858,7 @@
         <v>44774</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9931,7 +9931,7 @@
         <v>45764</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10004,7 +10004,7 @@
         <v>44994</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10077,7 +10077,7 @@
         <v>44937</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10150,7 +10150,7 @@
         <v>44645</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10228,7 +10228,7 @@
         <v>45170</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10301,7 +10301,7 @@
         <v>45887</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10379,7 +10379,7 @@
         <v>44836</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10452,7 +10452,7 @@
         <v>45722</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10525,7 +10525,7 @@
         <v>45167</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>45222</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10671,7 +10671,7 @@
         <v>44843</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10744,7 +10744,7 @@
         <v>44865</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>45887</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>45887</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>45887</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11051,7 +11051,7 @@
         <v>44638</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>45897</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45443</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11270,7 +11270,7 @@
         <v>45875</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11343,7 +11343,7 @@
         <v>44936</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11416,7 +11416,7 @@
         <v>45560</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>44812</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>45728</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45201</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45203</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44965</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44986</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45909</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45909</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45911</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12156,7 +12156,7 @@
         <v>44620</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12229,7 +12229,7 @@
         <v>45211</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12302,7 +12302,7 @@
         <v>45211</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12375,7 +12375,7 @@
         <v>45266</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12448,7 +12448,7 @@
         <v>44974</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12521,7 +12521,7 @@
         <v>44974</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>45070</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12672,7 +12672,7 @@
         <v>45131</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>45664</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12818,7 +12818,7 @@
         <v>44994</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>45033</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12964,7 +12964,7 @@
         <v>45558</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13037,7 +13037,7 @@
         <v>45210</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13110,7 +13110,7 @@
         <v>45210</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13183,7 +13183,7 @@
         <v>44943</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13256,7 +13256,7 @@
         <v>45343</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13329,7 +13329,7 @@
         <v>45720</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>45947</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13475,7 +13475,7 @@
         <v>44943</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13548,7 +13548,7 @@
         <v>45135</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13621,7 +13621,7 @@
         <v>44935</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13694,7 +13694,7 @@
         <v>46157</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13767,7 +13767,7 @@
         <v>45958</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13840,7 +13840,7 @@
         <v>45384</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13913,7 +13913,7 @@
         <v>46157</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>45958</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14059,7 +14059,7 @@
         <v>45958</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14132,7 +14132,7 @@
         <v>46142</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14210,7 +14210,7 @@
         <v>45965</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>45966</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14356,7 +14356,7 @@
         <v>45006</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14429,7 +14429,7 @@
         <v>45225</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14502,7 +14502,7 @@
         <v>45188</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14580,7 +14580,7 @@
         <v>45329</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14653,7 +14653,7 @@
         <v>46163</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14726,7 +14726,7 @@
         <v>46163</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14799,7 +14799,7 @@
         <v>46163</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14877,7 +14877,7 @@
         <v>44739</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14955,7 +14955,7 @@
         <v>45761</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15028,7 +15028,7 @@
         <v>45324</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>44756</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15179,7 +15179,7 @@
         <v>44936</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15252,7 +15252,7 @@
         <v>45639</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15325,7 +15325,7 @@
         <v>45535</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15398,7 +15398,7 @@
         <v>45243</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>45412</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15544,7 +15544,7 @@
         <v>45412</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15617,7 +15617,7 @@
         <v>45544</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15690,7 +15690,7 @@
         <v>45982</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15763,7 +15763,7 @@
         <v>45271</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45268</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15909,7 +15909,7 @@
         <v>45530</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -15982,7 +15982,7 @@
         <v>46169</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>44572</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16133,7 +16133,7 @@
         <v>44903</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>46003</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>46171</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16357,7 +16357,7 @@
         <v>46171</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16435,7 +16435,7 @@
         <v>46171</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16513,7 +16513,7 @@
         <v>45271</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16586,7 +16586,7 @@
         <v>46008</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16664,7 +16664,7 @@
         <v>44986</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16737,7 +16737,7 @@
         <v>45217</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>46171</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16888,7 +16888,7 @@
         <v>44930</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>45330</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17034,7 +17034,7 @@
         <v>46029</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17112,7 +17112,7 @@
         <v>46029</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17190,7 +17190,7 @@
         <v>45015</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17263,7 +17263,7 @@
         <v>44876</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17341,7 +17341,7 @@
         <v>44900</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>46042</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17487,7 +17487,7 @@
         <v>44812</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17560,7 +17560,7 @@
         <v>44957</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17633,7 +17633,7 @@
         <v>45371</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17706,7 +17706,7 @@
         <v>46050</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17779,7 +17779,7 @@
         <v>46051</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17857,7 +17857,7 @@
         <v>44622</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17930,7 +17930,7 @@
         <v>46057</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>46061</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18081,7 +18081,7 @@
         <v>45516</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18154,7 +18154,7 @@
         <v>46185</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>46188</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18305,7 +18305,7 @@
         <v>45271</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18378,7 +18378,7 @@
         <v>45268</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>46071</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18524,7 +18524,7 @@
         <v>46071</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18597,7 +18597,7 @@
         <v>46071</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45210</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>46077</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>46080</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18889,7 +18889,7 @@
         <v>45350</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18962,7 +18962,7 @@
         <v>45210</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19035,7 +19035,7 @@
         <v>46100</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>44993</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19181,7 +19181,7 @@
         <v>45702</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19259,7 +19259,7 @@
         <v>44890</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19332,7 +19332,7 @@
         <v>45761</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>46119</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19478,7 +19478,7 @@
         <v>44973</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>44614</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19629,7 +19629,7 @@
         <v>44816</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19702,7 +19702,7 @@
         <v>45583</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19775,7 +19775,7 @@
         <v>44943</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19848,7 +19848,7 @@
         <v>44981</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45210</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -19994,7 +19994,7 @@
         <v>44756</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20067,7 +20067,7 @@
         <v>45412</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20140,7 +20140,7 @@
         <v>45412</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>46205</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20286,7 +20286,7 @@
         <v>46199</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20359,7 +20359,7 @@
         <v>46199</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20432,7 +20432,7 @@
         <v>44965</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20505,7 +20505,7 @@
         <v>44496</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20578,7 +20578,7 @@
         <v>45200</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20651,7 +20651,7 @@
         <v>45590</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20729,7 +20729,7 @@
         <v>46199</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20802,7 +20802,7 @@
         <v>45709</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>46199</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>46206</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21026,7 +21026,7 @@
         <v>45211</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21099,7 +21099,7 @@
         <v>45114</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21172,7 +21172,7 @@
         <v>44489</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21250,7 +21250,7 @@
         <v>45289</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21328,7 +21328,7 @@
         <v>45548</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21401,7 +21401,7 @@
         <v>45211</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21474,7 +21474,7 @@
         <v>44881</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21547,7 +21547,7 @@
         <v>45460</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45524</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21693,7 +21693,7 @@
         <v>44553</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21766,7 +21766,7 @@
         <v>45590</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21844,7 +21844,7 @@
         <v>44649</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21917,7 +21917,7 @@
         <v>44617</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -21995,7 +21995,7 @@
         <v>45097</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22073,7 +22073,7 @@
         <v>45706</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45722</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22219,7 +22219,7 @@
         <v>44616</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22297,7 +22297,7 @@
         <v>45590</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45070</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22448,7 +22448,7 @@
         <v>45751</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>44999</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22594,7 +22594,7 @@
         <v>45200</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22667,7 +22667,7 @@
         <v>45528</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>45210</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>46288</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22891,7 +22891,7 @@
         <v>46288</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -22969,7 +22969,7 @@
         <v>46289</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23047,7 +23047,7 @@
         <v>46288</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>44848</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>46288</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23276,7 +23276,7 @@
         <v>46288</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>46288</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>46288</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23510,7 +23510,7 @@
         <v>45260</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45393</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23656,7 +23656,7 @@
         <v>46290</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45516</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23802,7 +23802,7 @@
         <v>44746</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23875,7 +23875,7 @@
         <v>46293</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23948,7 +23948,7 @@
         <v>45516</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45674</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>44917</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24167,7 +24167,7 @@
         <v>45691</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24240,7 +24240,7 @@
         <v>45265</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24318,7 +24318,7 @@
         <v>46253</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45211</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24464,7 +24464,7 @@
         <v>45720</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45299</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24610,7 +24610,7 @@
         <v>46300</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>45720</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>46300</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24829,7 +24829,7 @@
         <v>46300</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45684</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24980,7 +24980,7 @@
         <v>46300</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25053,7 +25053,7 @@
         <v>46300</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25126,7 +25126,7 @@
         <v>45307</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25199,7 +25199,7 @@
         <v>45516</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>45590</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25345,7 +25345,7 @@
         <v>45545</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>44521</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25491,7 +25491,7 @@
         <v>45705</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25564,7 +25564,7 @@
         <v>45616</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25637,7 +25637,7 @@
         <v>45211</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45728</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25788,7 +25788,7 @@
         <v>45502</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25861,7 +25861,7 @@
         <v>45709</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25934,7 +25934,7 @@
         <v>45790</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45716</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26080,7 +26080,7 @@
         <v>46261</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26158,7 +26158,7 @@
         <v>45331</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26231,7 +26231,7 @@
         <v>45610</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26304,7 +26304,7 @@
         <v>46261</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26382,7 +26382,7 @@
         <v>45600</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26455,7 +26455,7 @@
         <v>45798</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26533,7 +26533,7 @@
         <v>45798</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26611,7 +26611,7 @@
         <v>46262</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>46262</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26757,7 +26757,7 @@
         <v>45798</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>45804</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26913,7 +26913,7 @@
         <v>45804</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45804</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>45754</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45817</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45818</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45819</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45821</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45820</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>45820</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45827</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45832</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45873</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45875</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45618</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>45757</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>46064</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>

--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45708</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44648</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>44581</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44610</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45215</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45097</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44628</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45441</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46009</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>46300</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>45015</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>44524</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>44880</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45330</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45201</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44546</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45015</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>45035</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>45947</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>45181</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45716</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45821</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>45821</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45705</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>45210</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45162</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45761</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44972</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45716</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45821</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45703</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45703</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44619</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44746</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44523</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>44539</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44766</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44880</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44496</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44758</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>44693</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44880</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>44526</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>44523</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>44592</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>45887</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>45887</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45887</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44530</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45709</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>45887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>45590</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>45897</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45343</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45211</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44496</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>45299</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44964</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>45203</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44572</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>45412</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>45412</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44930</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>45909</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>44816</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>45909</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>45911</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>44937</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>46163</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>46163</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>46163</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45674</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45982</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45210</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>45114</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45705</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>46169</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45639</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44622</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45225</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>46171</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>46171</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44616</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45324</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>46171</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46171</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45530</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44848</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45373</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44812</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45393</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45460</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45097</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>44883</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45720</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45210</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44553</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>45131</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45947</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>44981</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>45329</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>45677</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45958</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>45201</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44974</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44974</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45958</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>45211</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>46185</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>46188</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45966</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45965</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44843</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44935</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45371</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45266</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45590</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>44890</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45070</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45289</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>44942</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>44774</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>44756</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>45600</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44812</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>46199</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>46199</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>45222</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>46199</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46205</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>46199</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44957</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>46206</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45343</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>45722</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45702</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45516</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45271</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45524</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45384</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45443</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45720</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>46003</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45684</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>46008</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45516</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45265</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45545</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45271</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45307</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45590</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45790</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>46029</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>46029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>45211</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44521</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45502</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45716</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45331</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45728</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45616</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45709</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>45705</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45271</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45600</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>46288</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>46288</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>46042</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45610</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>46288</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>46288</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45798</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45798</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45798</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>46288</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>46288</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>46288</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>46050</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>46051</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45804</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45804</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45804</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>46289</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>46057</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>46290</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45754</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>46293</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>46061</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45817</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45818</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>46071</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>45820</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>46071</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>46071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45820</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45819</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45821</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46077</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>46080</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45827</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46253</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46300</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46300</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>46300</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>46300</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46300</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>44521</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>46100</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45832</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>46119</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45243</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>46261</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45873</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>46261</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45875</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>46262</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>46262</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>44903</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45590</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45674</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45728</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>44943</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45260</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>45516</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45516</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>45167</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44999</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>45560</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44994</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45033</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45240</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44865</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45875</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45560</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45170</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>44936</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44965</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>44876</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45590</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45210</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45744</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45548</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>44936</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>45199</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44943</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44739</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44993</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45350</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44830</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45015</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>46142</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>46157</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>46157</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44971</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44614</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>44958</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>44965</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45006</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45706</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>44986</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>44881</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45664</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45722</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>44986</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45544</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44830</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45211</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>44746</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44843</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45070</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>44847</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45210</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45535</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>44943</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44901</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>44836</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>44994</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45211</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45200</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45393</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45268</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45163</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45412</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45412</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>45397</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>44620</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>45720</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>44536</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45470</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>44630</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45548</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45751</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>45330</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45590</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45217</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44649</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44629</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>44645</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44638</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>45200</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45691</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45761</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44574</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45210</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45210</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45764</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44900</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45188</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>44746</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44746</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44746</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44797</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45265</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45761</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>44693</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45324</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45583</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45135</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45528</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>44756</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45201</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45268</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44973</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45618</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45757</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>46064</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>

--- a/Översikt MARIESTAD.xlsx
+++ b/Översikt MARIESTAD.xlsx
@@ -601,7 +601,7 @@
         <v>46213</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -732,7 +732,7 @@
         <v>45691</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -849,7 +849,7 @@
         <v>45664</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
         <v>46279</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1077,7 +1077,7 @@
         <v>45708</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
         <v>44648</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1297,7 +1297,7 @@
         <v>44581</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1408,7 +1408,7 @@
         <v>44610</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>45215</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1628,7 +1628,7 @@
         <v>45097</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1734,7 +1734,7 @@
         <v>44628</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45441</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>46009</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2066,7 +2066,7 @@
         <v>46300</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2172,7 +2172,7 @@
         <v>45015</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2282,7 +2282,7 @@
         <v>44524</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>44880</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>45330</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         <v>45203</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2711,7 +2711,7 @@
         <v>45201</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>44546</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>45112</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3036,7 +3036,7 @@
         <v>45015</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3145,7 +3145,7 @@
         <v>45035</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3250,7 +3250,7 @@
         <v>45435</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3360,7 +3360,7 @@
         <v>45947</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3465,7 +3465,7 @@
         <v>45181</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3570,7 +3570,7 @@
         <v>45716</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3680,7 +3680,7 @@
         <v>45821</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>45821</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -3900,7 +3900,7 @@
         <v>45705</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4005,7 +4005,7 @@
         <v>45210</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45162</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4220,7 +4220,7 @@
         <v>45761</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4325,7 +4325,7 @@
         <v>44972</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4430,7 +4430,7 @@
         <v>45716</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
         <v>45797</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4645,7 +4645,7 @@
         <v>45821</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4755,7 +4755,7 @@
         <v>45703</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>45703</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -4975,7 +4975,7 @@
         <v>44619</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5048,7 +5048,7 @@
         <v>44574</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5121,7 +5121,7 @@
         <v>44746</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5194,7 +5194,7 @@
         <v>44840</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5267,7 +5267,7 @@
         <v>44852</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5340,7 +5340,7 @@
         <v>44523</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5413,7 +5413,7 @@
         <v>44539</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>44614</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5564,7 +5564,7 @@
         <v>44766</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -5637,7 +5637,7 @@
         <v>44880</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5710,7 +5710,7 @@
         <v>44496</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>44758</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -5861,7 +5861,7 @@
         <v>44693</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44649</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>44571</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6080,7 +6080,7 @@
         <v>44880</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6153,7 +6153,7 @@
         <v>44526</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6231,7 +6231,7 @@
         <v>44523</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>44592</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>45887</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -6455,7 +6455,7 @@
         <v>45887</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -6533,7 +6533,7 @@
         <v>45887</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>44530</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45709</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>45887</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>45590</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>45897</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>45343</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         <v>45211</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>44496</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -7205,7 +7205,7 @@
         <v>45299</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -7278,7 +7278,7 @@
         <v>44964</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>45203</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -7424,7 +7424,7 @@
         <v>44572</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -7502,7 +7502,7 @@
         <v>45412</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -7575,7 +7575,7 @@
         <v>45412</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>44617</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -7726,7 +7726,7 @@
         <v>44930</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -7799,7 +7799,7 @@
         <v>45909</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -7872,7 +7872,7 @@
         <v>44816</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -7945,7 +7945,7 @@
         <v>45909</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -8018,7 +8018,7 @@
         <v>45911</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -8091,7 +8091,7 @@
         <v>44937</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -8164,7 +8164,7 @@
         <v>46163</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -8242,7 +8242,7 @@
         <v>46163</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>46163</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         <v>45674</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>45982</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>45210</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -8607,7 +8607,7 @@
         <v>45114</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45705</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -8753,7 +8753,7 @@
         <v>46169</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -8826,7 +8826,7 @@
         <v>44917</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -8899,7 +8899,7 @@
         <v>45558</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -8972,7 +8972,7 @@
         <v>45639</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -9045,7 +9045,7 @@
         <v>44622</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45225</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>45097</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -9264,7 +9264,7 @@
         <v>46171</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>46171</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -9420,7 +9420,7 @@
         <v>44616</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -9498,7 +9498,7 @@
         <v>45324</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -9576,7 +9576,7 @@
         <v>46171</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>46171</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -9732,7 +9732,7 @@
         <v>45530</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44848</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -9878,7 +9878,7 @@
         <v>44536</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -9951,7 +9951,7 @@
         <v>45373</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -10024,7 +10024,7 @@
         <v>44812</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -10097,7 +10097,7 @@
         <v>45393</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>45460</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -10243,7 +10243,7 @@
         <v>45097</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>44883</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -10399,7 +10399,7 @@
         <v>45720</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>45210</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -10545,7 +10545,7 @@
         <v>44553</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -10618,7 +10618,7 @@
         <v>45131</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -10691,7 +10691,7 @@
         <v>45947</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -10764,7 +10764,7 @@
         <v>44981</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         <v>45329</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>45677</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -10983,7 +10983,7 @@
         <v>45958</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -11056,7 +11056,7 @@
         <v>45201</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -11129,7 +11129,7 @@
         <v>44974</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -11202,7 +11202,7 @@
         <v>44974</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45958</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -11348,7 +11348,7 @@
         <v>45958</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -11421,7 +11421,7 @@
         <v>45211</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -11494,7 +11494,7 @@
         <v>46185</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>46188</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -11645,7 +11645,7 @@
         <v>45966</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -11718,7 +11718,7 @@
         <v>45965</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -11791,7 +11791,7 @@
         <v>44843</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -11864,7 +11864,7 @@
         <v>44935</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>45371</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -12010,7 +12010,7 @@
         <v>45266</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -12083,7 +12083,7 @@
         <v>45590</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -12161,7 +12161,7 @@
         <v>44890</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -12234,7 +12234,7 @@
         <v>45070</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -12312,7 +12312,7 @@
         <v>45289</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -12390,7 +12390,7 @@
         <v>44942</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -12463,7 +12463,7 @@
         <v>44774</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -12536,7 +12536,7 @@
         <v>44756</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>45600</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12682,7 +12682,7 @@
         <v>44812</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>46199</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12828,7 +12828,7 @@
         <v>46199</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -12901,7 +12901,7 @@
         <v>45222</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -12974,7 +12974,7 @@
         <v>46199</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -13047,7 +13047,7 @@
         <v>46205</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>46199</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44957</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -13266,7 +13266,7 @@
         <v>46206</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -13344,7 +13344,7 @@
         <v>45343</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -13417,7 +13417,7 @@
         <v>45722</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -13490,7 +13490,7 @@
         <v>45702</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>45516</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -13641,7 +13641,7 @@
         <v>45271</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -13714,7 +13714,7 @@
         <v>45524</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -13787,7 +13787,7 @@
         <v>45384</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>45443</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>45720</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>46003</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -14079,7 +14079,7 @@
         <v>45684</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -14157,7 +14157,7 @@
         <v>46008</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -14235,7 +14235,7 @@
         <v>45516</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -14308,7 +14308,7 @@
         <v>45265</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45545</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>45271</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -14532,7 +14532,7 @@
         <v>45307</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -14605,7 +14605,7 @@
         <v>45590</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -14678,7 +14678,7 @@
         <v>45790</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -14751,7 +14751,7 @@
         <v>46029</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -14829,7 +14829,7 @@
         <v>46029</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -14907,7 +14907,7 @@
         <v>45211</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -14980,7 +14980,7 @@
         <v>44521</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -15053,7 +15053,7 @@
         <v>45502</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -15126,7 +15126,7 @@
         <v>45716</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -15199,7 +15199,7 @@
         <v>45331</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -15272,7 +15272,7 @@
         <v>45728</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -15350,7 +15350,7 @@
         <v>45616</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -15423,7 +15423,7 @@
         <v>45709</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -15496,7 +15496,7 @@
         <v>45705</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>45268</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -15642,7 +15642,7 @@
         <v>45271</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -15715,7 +15715,7 @@
         <v>45600</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -15788,7 +15788,7 @@
         <v>46288</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -15866,7 +15866,7 @@
         <v>46288</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -15944,7 +15944,7 @@
         <v>46042</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -16017,7 +16017,7 @@
         <v>45610</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -16090,7 +16090,7 @@
         <v>46288</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>46288</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -16246,7 +16246,7 @@
         <v>45798</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -16324,7 +16324,7 @@
         <v>45798</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -16402,7 +16402,7 @@
         <v>45798</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -16480,7 +16480,7 @@
         <v>46288</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>46288</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>46288</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -16714,7 +16714,7 @@
         <v>46050</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -16787,7 +16787,7 @@
         <v>46051</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -16865,7 +16865,7 @@
         <v>45804</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>45804</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -17016,7 +17016,7 @@
         <v>45804</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -17089,7 +17089,7 @@
         <v>46289</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>46057</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>46290</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45754</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>46293</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>46061</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>45817</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>45818</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>46071</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>45820</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>46071</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>46071</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45820</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>45819</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>45821</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>46077</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>46080</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45827</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>46253</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46300</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46300</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>46300</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>46300</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46300</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>44521</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>46100</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45832</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>46119</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45243</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>46261</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -19294,7 +19294,7 @@
         <v>45873</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>46261</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -19445,7 +19445,7 @@
         <v>45875</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -19523,7 +19523,7 @@
         <v>46262</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -19596,7 +19596,7 @@
         <v>46262</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -19669,7 +19669,7 @@
         <v>44903</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -19742,7 +19742,7 @@
         <v>45590</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -19820,7 +19820,7 @@
         <v>45674</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -19893,7 +19893,7 @@
         <v>45728</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -19971,7 +19971,7 @@
         <v>44943</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -20044,7 +20044,7 @@
         <v>45260</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -20117,7 +20117,7 @@
         <v>45516</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -20190,7 +20190,7 @@
         <v>45516</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -20263,7 +20263,7 @@
         <v>45167</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -20336,7 +20336,7 @@
         <v>44999</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -20409,7 +20409,7 @@
         <v>45560</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -20487,7 +20487,7 @@
         <v>44994</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -20560,7 +20560,7 @@
         <v>45033</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -20633,7 +20633,7 @@
         <v>45240</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -20706,7 +20706,7 @@
         <v>44865</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -20779,7 +20779,7 @@
         <v>45875</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45560</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -20930,7 +20930,7 @@
         <v>45170</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -21003,7 +21003,7 @@
         <v>44936</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -21076,7 +21076,7 @@
         <v>44965</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -21149,7 +21149,7 @@
         <v>44876</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45590</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -21305,7 +21305,7 @@
         <v>45210</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>45744</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -21451,7 +21451,7 @@
         <v>45548</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -21524,7 +21524,7 @@
         <v>44936</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -21597,7 +21597,7 @@
         <v>45199</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -21670,7 +21670,7 @@
         <v>44943</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>44739</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>44993</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -21899,7 +21899,7 @@
         <v>45350</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>44830</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>45015</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -22118,7 +22118,7 @@
         <v>46142</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>46157</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -22269,7 +22269,7 @@
         <v>46157</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -22342,7 +22342,7 @@
         <v>44971</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -22415,7 +22415,7 @@
         <v>44614</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -22493,7 +22493,7 @@
         <v>44958</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -22566,7 +22566,7 @@
         <v>44965</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -22639,7 +22639,7 @@
         <v>45006</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -22712,7 +22712,7 @@
         <v>45706</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>44986</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -22858,7 +22858,7 @@
         <v>44993</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -22931,7 +22931,7 @@
         <v>44881</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45664</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -23077,7 +23077,7 @@
         <v>45722</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -23150,7 +23150,7 @@
         <v>44986</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45544</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -23296,7 +23296,7 @@
         <v>45210</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -23369,7 +23369,7 @@
         <v>45210</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -23442,7 +23442,7 @@
         <v>44830</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -23515,7 +23515,7 @@
         <v>45211</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -23588,7 +23588,7 @@
         <v>44746</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>44843</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -23734,7 +23734,7 @@
         <v>45070</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -23807,7 +23807,7 @@
         <v>44847</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -23880,7 +23880,7 @@
         <v>45210</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45535</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -24026,7 +24026,7 @@
         <v>44943</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -24099,7 +24099,7 @@
         <v>44901</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -24177,7 +24177,7 @@
         <v>44836</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -24250,7 +24250,7 @@
         <v>44994</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -24323,7 +24323,7 @@
         <v>45211</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -24396,7 +24396,7 @@
         <v>45200</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>45393</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45268</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45163</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -24693,7 +24693,7 @@
         <v>45412</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -24766,7 +24766,7 @@
         <v>45412</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -24839,7 +24839,7 @@
         <v>45397</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>44620</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -24985,7 +24985,7 @@
         <v>45720</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -25058,7 +25058,7 @@
         <v>44536</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -25136,7 +25136,7 @@
         <v>45470</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -25214,7 +25214,7 @@
         <v>44630</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -25287,7 +25287,7 @@
         <v>45548</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -25360,7 +25360,7 @@
         <v>45751</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -25433,7 +25433,7 @@
         <v>45330</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -25506,7 +25506,7 @@
         <v>45590</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -25579,7 +25579,7 @@
         <v>45217</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -25652,7 +25652,7 @@
         <v>44649</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -25725,7 +25725,7 @@
         <v>44629</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -25803,7 +25803,7 @@
         <v>44645</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>44638</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -25954,7 +25954,7 @@
         <v>45200</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -26027,7 +26027,7 @@
         <v>45691</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -26100,7 +26100,7 @@
         <v>45761</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -26173,7 +26173,7 @@
         <v>44574</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -26246,7 +26246,7 @@
         <v>45210</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -26319,7 +26319,7 @@
         <v>45210</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -26392,7 +26392,7 @@
         <v>45764</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -26465,7 +26465,7 @@
         <v>44900</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -26538,7 +26538,7 @@
         <v>45188</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>44746</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>44746</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -26762,7 +26762,7 @@
         <v>44746</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -26835,7 +26835,7 @@
         <v>44797</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -26908,7 +26908,7 @@
         <v>45265</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45761</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -27059,7 +27059,7 @@
         <v>44693</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -27132,7 +27132,7 @@
         <v>45324</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -27205,7 +27205,7 @@
         <v>45211</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -27278,7 +27278,7 @@
         <v>45583</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45135</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -27424,7 +27424,7 @@
         <v>45528</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -27497,7 +27497,7 @@
         <v>44756</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -27570,7 +27570,7 @@
         <v>45201</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -27643,7 +27643,7 @@
         <v>45268</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>44973</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45618</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -27867,7 +27867,7 @@
         <v>45757</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -27945,7 +27945,7 @@
         <v>46064</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
